--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362994</v>
+        <v>122361949</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>90779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>A1764-2025, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590215</v>
+        <v>590270</v>
       </c>
       <c r="R2" t="n">
-        <v>6441152</v>
+        <v>6441156</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,25 +770,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361949</v>
+        <v>122362994</v>
       </c>
       <c r="B3" t="n">
-        <v>90779</v>
+        <v>98175</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,48 +812,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A1764-2025, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590270</v>
+        <v>590215</v>
       </c>
       <c r="R3" t="n">
-        <v>6441156</v>
+        <v>6441152</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,30 +896,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361949</v>
+        <v>122362994</v>
       </c>
       <c r="B2" t="n">
-        <v>90779</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A1764-2025, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590270</v>
+        <v>590215</v>
       </c>
       <c r="R2" t="n">
-        <v>6441156</v>
+        <v>6441152</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,40 +771,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362994</v>
+        <v>122361949</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>90789</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,49 +798,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>A1764-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590215</v>
+        <v>590270</v>
       </c>
       <c r="R3" t="n">
-        <v>6441152</v>
+        <v>6441156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,18 +881,147 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122435239</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91194</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 1767, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590229</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6441136</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362994</v>
+        <v>122361949</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>90801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>A1764-2025, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590215</v>
+        <v>590270</v>
       </c>
       <c r="R2" t="n">
-        <v>6441152</v>
+        <v>6441156</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,25 +770,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361949</v>
+        <v>122362994</v>
       </c>
       <c r="B3" t="n">
-        <v>90789</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,48 +812,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A1764-2025, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590270</v>
+        <v>590215</v>
       </c>
       <c r="R3" t="n">
-        <v>6441156</v>
+        <v>6441152</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,30 +896,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -914,7 +914,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91194</v>
+        <v>91206</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361949</v>
+        <v>122362994</v>
       </c>
       <c r="B2" t="n">
-        <v>90801</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A1764-2025, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590270</v>
+        <v>590215</v>
       </c>
       <c r="R2" t="n">
-        <v>6441156</v>
+        <v>6441152</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,40 +771,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362994</v>
+        <v>122361949</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>90808</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,49 +798,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>A1764-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590215</v>
+        <v>590270</v>
       </c>
       <c r="R3" t="n">
-        <v>6441152</v>
+        <v>6441156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,15 +881,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -914,7 +914,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91206</v>
+        <v>91211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122362994</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -789,7 +784,7 @@
         <v>122361949</v>
       </c>
       <c r="B3" t="n">
-        <v>90808</v>
+        <v>90813</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,11 +798,6 @@
       </c>
       <c r="E3" t="n">
         <v>1202</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -880,11 +870,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -914,7 +899,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91211</v>
+        <v>91216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,11 +913,6 @@
       </c>
       <c r="E4" t="n">
         <v>5420</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122362994</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -784,7 +789,7 @@
         <v>122361949</v>
       </c>
       <c r="B3" t="n">
-        <v>90813</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,6 +803,11 @@
       </c>
       <c r="E3" t="n">
         <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -870,6 +880,11 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -899,7 +914,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91216</v>
+        <v>91229</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,6 +928,11 @@
       </c>
       <c r="E4" t="n">
         <v>5420</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362994</v>
+        <v>122361949</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>90839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>A1764-2025, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590215</v>
+        <v>590270</v>
       </c>
       <c r="R2" t="n">
-        <v>6441152</v>
+        <v>6441156</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,25 +770,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361949</v>
+        <v>122362994</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,48 +812,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A1764-2025, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590270</v>
+        <v>590215</v>
       </c>
       <c r="R3" t="n">
-        <v>6441156</v>
+        <v>6441152</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,30 +896,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -914,7 +914,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91229</v>
+        <v>91242</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361949</v>
+        <v>122362994</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A1764-2025, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590270</v>
+        <v>590215</v>
       </c>
       <c r="R2" t="n">
-        <v>6441156</v>
+        <v>6441152</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,40 +771,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362994</v>
+        <v>122361949</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,49 +798,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>A1764-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590215</v>
+        <v>590270</v>
       </c>
       <c r="R3" t="n">
-        <v>6441152</v>
+        <v>6441156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,15 +881,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -914,7 +914,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91242</v>
+        <v>91243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122362994</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>122361949</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91243</v>
+        <v>91244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122362994</v>
+        <v>122361949</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>A1764-2025, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590215</v>
+        <v>590270</v>
       </c>
       <c r="R2" t="n">
-        <v>6441152</v>
+        <v>6441156</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,25 +770,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122361949</v>
+        <v>122362994</v>
       </c>
       <c r="B3" t="n">
-        <v>90834</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,48 +812,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A1764-2025, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590270</v>
+        <v>590215</v>
       </c>
       <c r="R3" t="n">
-        <v>6441156</v>
+        <v>6441152</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,30 +896,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -914,7 +914,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91244</v>
+        <v>91247</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122361949</v>
+        <v>122362994</v>
       </c>
       <c r="B2" t="n">
-        <v>90837</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A1764-2025, Sm</t>
+          <t>A 1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590270</v>
+        <v>590215</v>
       </c>
       <c r="R2" t="n">
-        <v>6441156</v>
+        <v>6441152</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,40 +771,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122362994</v>
+        <v>122361949</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,49 +798,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1779, Svartgöl, Sm</t>
+          <t>A1764-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590215</v>
+        <v>590270</v>
       </c>
       <c r="R3" t="n">
-        <v>6441152</v>
+        <v>6441156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,15 +881,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 1764-2025 artfynd.xlsx
+++ b/artfynd/A 1764-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>122435239</v>
       </c>
       <c r="B4" t="n">
-        <v>91247</v>
+        <v>91350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
